--- a/download/predictions_prophet.xlsx
+++ b/download/predictions_prophet.xlsx
@@ -537,22 +537,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4173</v>
+        <v>4279</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>3781</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1641</v>
+        <v>1667</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1601</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
@@ -562,22 +562,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8749</v>
+        <v>8250</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4942</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1810</v>
+        <v>1819</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>2093</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -587,22 +587,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>6004</v>
+        <v>5815</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>5015</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2056</v>
+        <v>2008</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>2124</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2564</v>
+        <v>2537</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>6099</v>
@@ -621,7 +621,7 @@
         <v>42</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>2582</v>
@@ -637,16 +637,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>21490</v>
+        <v>20882</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>19837</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>6275</v>
+        <v>6261</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>8400</v>
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>201.3</v>
+        <v>204</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>115.4</v>
+        <v>119.6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>294.6</v>
+        <v>292.4</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
@@ -810,19 +810,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>170.8</v>
+        <v>173.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>88.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>263.8</v>
+        <v>257.5</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>165.3</v>
+        <v>168</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>78</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>249.2</v>
+        <v>255.1</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
@@ -864,19 +864,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>169.3</v>
+        <v>171.9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>253.6</v>
+        <v>263</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>124.7</v>
+        <v>127.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>36.8</v>
+        <v>43.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>214.3</v>
+        <v>222.2</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-94.2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>126</v>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>203.6</v>
+        <v>206.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>113.3</v>
+        <v>117.5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>284.3</v>
+        <v>287.3</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -972,19 +972,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>176</v>
+        <v>178.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>87.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>261.5</v>
+        <v>269.7</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>142.4</v>
+        <v>145.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>58.7</v>
+        <v>60.3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>237.8</v>
+        <v>239.8</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>134.4</v>
+        <v>137.2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>44.8</v>
+        <v>47.6</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>217.9</v>
+        <v>229.2</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>136.9</v>
+        <v>139.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>45.1</v>
+        <v>49.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>219.4</v>
+        <v>216</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.8</v>
+        <v>7.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>172.4</v>
+        <v>182.6</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-120.3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>57.6</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>173.1</v>
+        <v>176</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>81.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>256</v>
+        <v>258.7</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>148.3</v>
+        <v>151.3</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>58.1</v>
+        <v>65.8</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>243</v>
+        <v>242.6</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>118.7</v>
+        <v>121.7</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>34.3</v>
+        <v>30.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>206.9</v>
+        <v>200.2</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>115.9</v>
+        <v>118.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>30.9</v>
+        <v>30.1</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>204.7</v>
+        <v>213.2</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>124.4</v>
+        <v>127.5</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>34.7</v>
+        <v>42.6</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>209.2</v>
+        <v>218.9</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>86.5</v>
+        <v>89.8</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3</v>
+        <v>7.5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>176.8</v>
+        <v>192</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-29.5</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-117</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>184.1</v>
+        <v>187.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>91.5</v>
+        <v>105.4</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>264.4</v>
+        <v>273.6</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26">
@@ -1350,19 +1350,19 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>168.4</v>
+        <v>171.8</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>91.3</v>
+        <v>81.7</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>259.8</v>
+        <v>267.1</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>148.2</v>
+        <v>151.6</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>62.3</v>
+        <v>66.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>237</v>
+        <v>240.8</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
@@ -1404,19 +1404,19 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>154.8</v>
+        <v>158.3</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>66</v>
+        <v>70.7</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>244.9</v>
+        <v>242.3</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>172.8</v>
+        <v>176.3</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>90</v>
+        <v>86.2</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>259.7</v>
+        <v>261.3</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30">
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>144</v>
+        <v>147.6</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>56.9</v>
+        <v>48</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>224.9</v>
+        <v>234.9</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>36.6</v>
+        <v>0</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>122.5</v>
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1512,19 +1512,19 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>258.1</v>
+        <v>261.7</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>170.9</v>
+        <v>174.3</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>345.8</v>
+        <v>353.6</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33">
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>249.4</v>
+        <v>253.1</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>171</v>
+        <v>166.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>339.7</v>
+        <v>341.8</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34">
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>235.1</v>
+        <v>238.8</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>148.1</v>
+        <v>152.8</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>315.5</v>
+        <v>321.2</v>
       </c>
       <c r="F34" s="4" t="n">
         <v>126</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35">
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>246.4</v>
+        <v>250.1</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>155.8</v>
+        <v>158</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>335.5</v>
+        <v>335.6</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36">
@@ -1620,19 +1620,19 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>267.8</v>
+        <v>271.5</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>177.5</v>
+        <v>189.8</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>353</v>
+        <v>359.9</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37">
@@ -1647,19 +1647,19 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>240.9</v>
+        <v>244.8</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>152.2</v>
+        <v>157.8</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>330.1</v>
+        <v>325.8</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38">
@@ -1674,19 +1674,19 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>226.5</v>
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1701,19 +1701,19 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>354.4</v>
+        <v>358.2</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>263.7</v>
+        <v>273.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>447.3</v>
+        <v>446.8</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40">
@@ -1728,19 +1728,19 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>343</v>
+        <v>346.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>264.7</v>
+        <v>256</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>431.9</v>
+        <v>433.9</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41">
@@ -1755,19 +1755,19 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>324.6</v>
+        <v>328.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>239.4</v>
+        <v>244.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>409.4</v>
+        <v>415.8</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42">
@@ -1782,19 +1782,19 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>330.3</v>
+        <v>334.1</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>250.9</v>
+        <v>243.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>419.3</v>
+        <v>422.4</v>
       </c>
       <c r="F42" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>344.8</v>
+        <v>348.5</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>261.4</v>
+        <v>262.1</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>438.6</v>
+        <v>434.7</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44">
@@ -1836,19 +1836,19 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>309.7</v>
+        <v>313.6</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>226.7</v>
+        <v>225.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>399.2</v>
+        <v>407.1</v>
       </c>
       <c r="F44" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45">
@@ -1863,19 +1863,19 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>193.5</v>
+        <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>285.8</v>
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1890,19 +1890,19 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>403.7</v>
+        <v>407.5</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>313.7</v>
+        <v>322.4</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>489.3</v>
+        <v>498.5</v>
       </c>
       <c r="F46" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47">
@@ -1917,19 +1917,19 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>381.5</v>
+        <v>385.4</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>299.1</v>
+        <v>296.6</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>469.7</v>
+        <v>474.3</v>
       </c>
       <c r="F47" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48">
@@ -1944,19 +1944,19 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>351.7</v>
+        <v>355.5</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>263.1</v>
+        <v>269.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>436.7</v>
+        <v>442.5</v>
       </c>
       <c r="F48" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49">
@@ -1971,19 +1971,19 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>345.9</v>
+        <v>349.7</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>258.5</v>
+        <v>257.4</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>432.6</v>
+        <v>436</v>
       </c>
       <c r="F49" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50">
@@ -1998,19 +1998,19 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>348.6</v>
+        <v>352.4</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>264</v>
+        <v>265.9</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>435</v>
+        <v>440.1</v>
       </c>
       <c r="F50" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51">
@@ -2025,19 +2025,19 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>302.1</v>
+        <v>306.1</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>209.9</v>
+        <v>222.8</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>387</v>
+        <v>397.6</v>
       </c>
       <c r="F51" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52">
@@ -2052,19 +2052,19 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>174.8</v>
+        <v>0</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>263.5</v>
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2079,19 +2079,19 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>374.5</v>
+        <v>378.5</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>287.7</v>
+        <v>299.3</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>466</v>
+        <v>472.8</v>
       </c>
       <c r="F53" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54">
@@ -2106,19 +2106,19 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>342.6</v>
+        <v>346.7</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>260.3</v>
+        <v>249.6</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>423.8</v>
+        <v>435.5</v>
       </c>
       <c r="F54" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55">
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>304.1</v>
+        <v>308.1</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>227.3</v>
+        <v>224.4</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>392</v>
+        <v>395.4</v>
       </c>
       <c r="F55" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56">
@@ -2160,19 +2160,19 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>290.6</v>
+        <v>294.7</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>205</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>378.7</v>
+        <v>388.3</v>
       </c>
       <c r="F56" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57">
@@ -2187,19 +2187,19 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>287</v>
+        <v>291.1</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>195.1</v>
+        <v>197.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>367.3</v>
+        <v>379.6</v>
       </c>
       <c r="F57" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58">
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>235.4</v>
+        <v>239.7</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>147</v>
+        <v>150.5</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>319.8</v>
+        <v>327</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59">
@@ -2241,19 +2241,19 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>104.4</v>
+        <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>188.7</v>
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2268,19 +2268,19 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>301.9</v>
+        <v>306.2</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>216.4</v>
+        <v>214.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>392.7</v>
+        <v>394.2</v>
       </c>
       <c r="F60" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="61">
@@ -2295,19 +2295,19 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>269.2</v>
+        <v>273.6</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>182.7</v>
+        <v>186.8</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>355.5</v>
+        <v>361.5</v>
       </c>
       <c r="F61" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62">
@@ -2322,19 +2322,19 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>231.2</v>
+        <v>235.6</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>143.2</v>
+        <v>146.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>321.6</v>
+        <v>325.2</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63">
@@ -2349,19 +2349,19 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>219.6</v>
+        <v>224</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>135.2</v>
+        <v>141</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>299.4</v>
+        <v>313.3</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64">
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>219.1</v>
+        <v>223.5</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>135.2</v>
+        <v>143.2</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>304.7</v>
+        <v>313.3</v>
       </c>
       <c r="F64" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65">
@@ -2403,19 +2403,19 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>171.7</v>
+        <v>176.3</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>259.6</v>
+        <v>264.9</v>
       </c>
       <c r="F65" s="4" t="n">
         <v>164.7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66">
@@ -2430,19 +2430,19 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>45.9</v>
+        <v>0</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-33.3</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>136.1</v>
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2457,19 +2457,19 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>249.5</v>
+        <v>254.1</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>170.3</v>
+        <v>165.8</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>330.6</v>
+        <v>340.4</v>
       </c>
       <c r="F67" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68">
@@ -2484,19 +2484,19 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>223.4</v>
+        <v>228.1</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>133.7</v>
+        <v>139</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>307.1</v>
+        <v>313.1</v>
       </c>
       <c r="F68" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69">
@@ -2511,19 +2511,19 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>192.6</v>
+        <v>197.2</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>104.7</v>
+        <v>107.9</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>281.2</v>
+        <v>279.5</v>
       </c>
       <c r="F69" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70">
@@ -2538,19 +2538,19 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>188.4</v>
+        <v>193.1</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>104.3</v>
+        <v>111.1</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>275.7</v>
+        <v>280.6</v>
       </c>
       <c r="F70" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71">
@@ -2565,19 +2565,19 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>195.4</v>
+        <v>200.1</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>112.1</v>
+        <v>109.5</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>286.4</v>
+        <v>292</v>
       </c>
       <c r="F71" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="72">
@@ -2592,19 +2592,19 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>155.6</v>
+        <v>160.4</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>66</v>
+        <v>75.3</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>240.8</v>
+        <v>241.3</v>
       </c>
       <c r="F72" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73">
@@ -2619,19 +2619,19 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>126.2</v>
+        <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2646,19 +2646,19 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>247.4</v>
+        <v>252.2</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>161.8</v>
+        <v>165.7</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>335</v>
+        <v>340.4</v>
       </c>
       <c r="F74" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75">
@@ -2673,19 +2673,19 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>227.8</v>
+        <v>232.6</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>142.4</v>
+        <v>148.2</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>315.3</v>
+        <v>322.6</v>
       </c>
       <c r="F75" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76">
@@ -2700,19 +2700,19 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>202.6</v>
+        <v>207.4</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>116.1</v>
+        <v>121.6</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>289.1</v>
+        <v>291.2</v>
       </c>
       <c r="F76" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77">
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>203.5</v>
+        <v>208.2</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>121.6</v>
+        <v>120.9</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>291.4</v>
+        <v>294.5</v>
       </c>
       <c r="F77" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>214.7</v>
+        <v>219.4</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>132.3</v>
+        <v>133.2</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>296.9</v>
+        <v>296</v>
       </c>
       <c r="F78" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>178.1</v>
+        <v>183</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>85</v>
+        <v>87.2</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>266.9</v>
+        <v>273.2</v>
       </c>
       <c r="F79" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80">
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>62.1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-22.9</v>
+        <v>0</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>274.1</v>
+        <v>278.9</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>184.2</v>
+        <v>186.6</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>363.4</v>
+        <v>362.6</v>
       </c>
       <c r="F81" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82">
@@ -2862,19 +2862,19 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>255.1</v>
+        <v>260</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>169.8</v>
+        <v>173.4</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>341.2</v>
+        <v>350.9</v>
       </c>
       <c r="F82" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83">
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>229.9</v>
+        <v>234.8</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>140.3</v>
+        <v>145.9</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>319.3</v>
+        <v>322.3</v>
       </c>
       <c r="F83" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84">
@@ -2916,19 +2916,19 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>230</v>
+        <v>234.8</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>143.1</v>
+        <v>142.4</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>316.5</v>
+        <v>314.7</v>
       </c>
       <c r="F84" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85">
@@ -2943,19 +2943,19 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>239.7</v>
+        <v>244.6</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>148.5</v>
+        <v>156</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>326.4</v>
+        <v>331</v>
       </c>
       <c r="F85" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86">
@@ -2970,19 +2970,19 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>201.2</v>
+        <v>206.2</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>114.6</v>
+        <v>114.3</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>285.5</v>
+        <v>291.4</v>
       </c>
       <c r="F86" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87">
@@ -2997,19 +2997,19 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>82.7</v>
+        <v>0</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>-10.4</v>
+        <v>0</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>174.4</v>
+        <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3024,19 +3024,19 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>291.9</v>
+        <v>296.9</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>203.9</v>
+        <v>208.6</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>381.4</v>
+        <v>384.4</v>
       </c>
       <c r="F88" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="89">
@@ -3051,19 +3051,19 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>184.4</v>
+        <v>180.8</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>362.1</v>
+        <v>361.1</v>
       </c>
       <c r="F89" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>241.8</v>
+        <v>246.8</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>152.1</v>
+        <v>159.1</v>
       </c>
       <c r="E90" s="4" t="n">
         <v>331</v>
@@ -3090,7 +3090,7 @@
         <v>167.2</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91">
@@ -3105,19 +3105,19 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>238.8</v>
+        <v>243.9</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>153.2</v>
+        <v>149.6</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>325.3</v>
+        <v>326.8</v>
       </c>
       <c r="F91" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>245.7</v>
+        <v>250.8</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>156.6</v>
+        <v>161.7</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>333.1</v>
+        <v>342.2</v>
       </c>
       <c r="F92" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93">
@@ -3159,19 +3159,19 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>204.6</v>
+        <v>209.9</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>119.3</v>
+        <v>120.6</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>291.7</v>
+        <v>291.3</v>
       </c>
       <c r="F93" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94">
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>83.8</v>
+        <v>0</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>173.1</v>
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3213,19 +3213,19 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>291.2</v>
+        <v>296.5</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>201</v>
+        <v>203.8</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>382.2</v>
+        <v>384.2</v>
       </c>
       <c r="F95" s="4" t="n">
         <v>167.2</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96">
@@ -3240,19 +3240,19 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>267.8</v>
+        <v>273.2</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>182.2</v>
+        <v>185.7</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>357.1</v>
+        <v>358.5</v>
       </c>
       <c r="F96" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97">
@@ -3267,19 +3267,19 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>238.7</v>
+        <v>244.1</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>149.6</v>
+        <v>163.5</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>326.6</v>
+        <v>327.3</v>
       </c>
       <c r="F97" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="98">
@@ -3294,19 +3294,19 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>235.4</v>
+        <v>240.8</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>151.9</v>
+        <v>150.5</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>319.2</v>
+        <v>333.3</v>
       </c>
       <c r="F98" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99">
@@ -3321,19 +3321,19 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>242.4</v>
+        <v>247.9</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>156.7</v>
+        <v>168.3</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>339.1</v>
+        <v>339</v>
       </c>
       <c r="F99" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100">
@@ -3348,19 +3348,19 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>201.9</v>
+        <v>207.5</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>117.2</v>
+        <v>122.4</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>290.5</v>
+        <v>297.4</v>
       </c>
       <c r="F100" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101">
@@ -3375,19 +3375,19 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>-6.1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>171.2</v>
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3402,19 +3402,19 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>291</v>
+        <v>296.7</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>208</v>
+        <v>214.1</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>372.1</v>
+        <v>381.9</v>
       </c>
       <c r="F102" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103">
@@ -3429,19 +3429,19 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>269.5</v>
+        <v>275.2</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>183.6</v>
+        <v>189.4</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>357.3</v>
+        <v>362.6</v>
       </c>
       <c r="F103" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="104">
@@ -3456,19 +3456,19 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>242.5</v>
+        <v>248.2</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>154.1</v>
+        <v>156.5</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>333.4</v>
+        <v>335.7</v>
       </c>
       <c r="F104" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105">
@@ -3483,19 +3483,19 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>241.4</v>
+        <v>247.1</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>150.6</v>
+        <v>158.8</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>329.4</v>
+        <v>335.7</v>
       </c>
       <c r="F105" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106">
@@ -3510,19 +3510,19 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>250.8</v>
+        <v>256.5</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>164.2</v>
+        <v>171.1</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>339</v>
+        <v>342.4</v>
       </c>
       <c r="F106" s="4" t="n">
         <v>203.3</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="109">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>4173</v>
+        <v>4279</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1555</v>
+        <v>1996</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>6794</v>
+        <v>6577</v>
       </c>
       <c r="E111" s="4" t="n">
         <v>3781</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="112">
@@ -3593,19 +3593,19 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>8749</v>
+        <v>8250</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>6075</v>
+        <v>5899</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>11460</v>
+        <v>10642</v>
       </c>
       <c r="E112" s="4" t="n">
         <v>4942</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113">
@@ -3615,19 +3615,19 @@
         </is>
       </c>
       <c r="B113" s="4" t="n">
-        <v>6004</v>
+        <v>5815</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>3403</v>
+        <v>3588</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>8635</v>
+        <v>7959</v>
       </c>
       <c r="E113" s="4" t="n">
         <v>5015</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>2564</v>
+        <v>2537</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>1612</v>
+        <v>1680</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>3535</v>
+        <v>3414</v>
       </c>
       <c r="E114" s="4" t="n">
         <v>6099</v>
@@ -3738,19 +3738,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>53.2</v>
+        <v>55.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
@@ -3765,19 +3765,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>65.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>86.3</v>
+        <v>88.7</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
@@ -3792,19 +3792,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>57</v>
+        <v>58.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>36.2</v>
+        <v>37.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>78.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
@@ -3819,19 +3819,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>58.2</v>
+        <v>59.6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>35.9</v>
+        <v>37.9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>81.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
@@ -3846,19 +3846,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>43.6</v>
+        <v>45</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -3873,19 +3873,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-20.3</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3900,19 +3900,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>81.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>60.8</v>
+        <v>59.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>102.5</v>
+        <v>105.5</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -3927,19 +3927,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>49.4</v>
+        <v>51.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>94.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -3954,19 +3954,19 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>62.3</v>
+        <v>63.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>83</v>
+        <v>87.3</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -3981,19 +3981,19 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>32.4</v>
+        <v>33.7</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>77.2</v>
+        <v>78.3</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -4008,19 +4008,19 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>54.9</v>
+        <v>56.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>32.9</v>
+        <v>35.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
@@ -4035,19 +4035,19 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>64.2</v>
+        <v>64</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -4062,13 +4062,13 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-21.5</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>53.4</v>
@@ -4089,19 +4089,19 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>79.3</v>
+        <v>80.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>100</v>
+        <v>101.9</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19">
@@ -4116,19 +4116,19 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>69.5</v>
+        <v>70.8</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>46.9</v>
+        <v>48.8</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
@@ -4143,19 +4143,19 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>61</v>
+        <v>62.4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>41.2</v>
+        <v>39.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
@@ -4170,19 +4170,19 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>52.9</v>
+        <v>54.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>73.2</v>
+        <v>76.5</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22">
@@ -4197,19 +4197,19 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>54.8</v>
+        <v>56.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23">
@@ -4224,19 +4224,19 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>41.1</v>
+        <v>42.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>63.5</v>
+        <v>65</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
@@ -4251,19 +4251,19 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-20.2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>60.9</v>
+        <v>60.3</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>101</v>
+        <v>103.3</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26">
@@ -4305,19 +4305,19 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>50.6</v>
+        <v>51.7</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27">
@@ -4332,19 +4332,19 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>63.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>42.7</v>
+        <v>43.3</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
@@ -4359,19 +4359,19 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>56.4</v>
+        <v>57.7</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>33.8</v>
+        <v>35.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>79.3</v>
+        <v>82.2</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29">
@@ -4386,19 +4386,19 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>58.7</v>
+        <v>60.1</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>36.1</v>
+        <v>39.4</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>79.2</v>
+        <v>83.8</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30">
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>45.5</v>
+        <v>46.8</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>25.2</v>
+        <v>24.2</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
@@ -4440,19 +4440,19 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-15.9</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4467,19 +4467,19 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>85.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>62.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>106.6</v>
+        <v>110.1</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33">
@@ -4494,19 +4494,19 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>76.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>53.7</v>
+        <v>56.4</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>98.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34">
@@ -4521,19 +4521,19 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>68.8</v>
+        <v>70.3</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>48.5</v>
+        <v>47.2</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>91.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F34" s="4" t="n">
         <v>53.4</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35">
@@ -4548,19 +4548,19 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>61.1</v>
+        <v>62.5</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>39.9</v>
+        <v>40.2</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36">
@@ -4575,19 +4575,19 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>63.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>39.9</v>
+        <v>41.8</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>85.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>49.6</v>
+        <v>51</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>70.7</v>
+        <v>73.5</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38">
@@ -4629,19 +4629,19 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-11.2</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4656,19 +4656,19 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>89.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>110.8</v>
+        <v>113.2</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40">
@@ -4683,19 +4683,19 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>79.5</v>
+        <v>80.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>57.1</v>
+        <v>59.3</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>101.4</v>
+        <v>103.6</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41">
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>47.7</v>
+        <v>51.5</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>91.8</v>
+        <v>95.2</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42">
@@ -4737,19 +4737,19 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>62.6</v>
+        <v>64</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>83.8</v>
+        <v>86.8</v>
       </c>
       <c r="F42" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
@@ -4764,19 +4764,19 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>42.4</v>
+        <v>43.6</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44">
@@ -4791,19 +4791,19 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>49.8</v>
+        <v>51.2</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>71.7</v>
+        <v>73.8</v>
       </c>
       <c r="F44" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
@@ -4818,19 +4818,19 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>-12.4</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4845,19 +4845,19 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>88.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>108.4</v>
+        <v>111.1</v>
       </c>
       <c r="F46" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47">
@@ -4872,19 +4872,19 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>55.3</v>
+        <v>57</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>98.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F47" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48">
@@ -4899,19 +4899,19 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>68.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>46.8</v>
+        <v>47.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F48" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49">
@@ -4926,19 +4926,19 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>60.1</v>
+        <v>61.5</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>39.3</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>81.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="F49" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50">
@@ -4953,19 +4953,19 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>61.3</v>
+        <v>62.8</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>38</v>
+        <v>41.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>83.2</v>
+        <v>84.3</v>
       </c>
       <c r="F50" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51">
@@ -4980,19 +4980,19 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>46.8</v>
+        <v>48.2</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="F51" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52">
@@ -5007,19 +5007,19 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-16.9</v>
+        <v>0</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5034,19 +5034,19 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>63.2</v>
+        <v>63.6</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>106.7</v>
+        <v>108.1</v>
       </c>
       <c r="F53" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54">
@@ -5061,19 +5061,19 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>52.6</v>
+        <v>54.2</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>97.8</v>
+        <v>99.2</v>
       </c>
       <c r="F54" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55">
@@ -5088,19 +5088,19 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>43.9</v>
+        <v>46.8</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>88.3</v>
+        <v>89.8</v>
       </c>
       <c r="F55" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -5115,19 +5115,19 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>57.8</v>
+        <v>59.1</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>36</v>
+        <v>37.7</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="F56" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57">
@@ -5142,19 +5142,19 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>59.3</v>
+        <v>60.8</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>38.8</v>
+        <v>39.3</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>81.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F57" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58">
@@ -5169,19 +5169,19 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>45.4</v>
+        <v>46.8</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>23.5</v>
+        <v>24.7</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>67.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59">
@@ -5196,19 +5196,19 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>-15.9</v>
+        <v>0</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5223,19 +5223,19 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>63.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>105.7</v>
+        <v>107.5</v>
       </c>
       <c r="F60" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61">
@@ -5250,19 +5250,19 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>75.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>52.7</v>
+        <v>54.4</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F61" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62">
@@ -5277,19 +5277,19 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>43.6</v>
+        <v>48.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>88.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
@@ -5304,19 +5304,19 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>59.7</v>
+        <v>61.1</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>38.6</v>
+        <v>39.7</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>80.2</v>
+        <v>83.3</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64">
@@ -5331,19 +5331,19 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>62.1</v>
+        <v>63.5</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>41.4</v>
+        <v>40.7</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F64" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
@@ -5358,19 +5358,19 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>48.8</v>
+        <v>50.2</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>28.2</v>
+        <v>30.4</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>70.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F65" s="4" t="n">
         <v>69.8</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66">
@@ -5385,19 +5385,19 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-12.3</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5412,19 +5412,19 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>89.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>112.5</v>
+        <v>112.8</v>
       </c>
       <c r="F67" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68">
@@ -5439,19 +5439,19 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>80.8</v>
+        <v>82.2</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>102.6</v>
+        <v>103.4</v>
       </c>
       <c r="F68" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69">
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>73.2</v>
+        <v>74.8</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>50.9</v>
+        <v>53.2</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>94.7</v>
+        <v>97.3</v>
       </c>
       <c r="F69" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70">
@@ -5493,19 +5493,19 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>66</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>44.1</v>
+        <v>46</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>88</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F70" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71">
@@ -5520,19 +5520,19 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>68.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>45.9</v>
+        <v>48.5</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>88.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F71" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72">
@@ -5547,19 +5547,19 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>77.7</v>
+        <v>78.7</v>
       </c>
       <c r="F72" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73">
@@ -5574,19 +5574,19 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>-6.4</v>
+        <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>37.2</v>
+        <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -5601,19 +5601,19 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>96.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>117.5</v>
+        <v>120</v>
       </c>
       <c r="F74" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75">
@@ -5628,19 +5628,19 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>87.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>65.7</v>
+        <v>68.3</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>108.9</v>
+        <v>110</v>
       </c>
       <c r="F75" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76">
@@ -5655,19 +5655,19 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>79.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>59.7</v>
+        <v>59.4</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>100.6</v>
+        <v>103.9</v>
       </c>
       <c r="F76" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77">
@@ -5682,19 +5682,19 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>72.3</v>
+        <v>73.8</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>51.6</v>
+        <v>53.7</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="F77" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78">
@@ -5709,19 +5709,19 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>74.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>51.8</v>
+        <v>52.9</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79">
@@ -5736,19 +5736,19 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>61.1</v>
+        <v>62.6</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>40.6</v>
+        <v>41.7</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>84</v>
+        <v>84.3</v>
       </c>
       <c r="F79" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80">
@@ -5763,19 +5763,19 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>42.6</v>
+        <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5790,19 +5790,19 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>100.9</v>
+        <v>102.4</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>79.5</v>
+        <v>79.2</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>122.6</v>
+        <v>124.4</v>
       </c>
       <c r="F81" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82">
@@ -5817,19 +5817,19 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>91.3</v>
+        <v>92.8</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>69.8</v>
+        <v>72</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>112.3</v>
+        <v>113.5</v>
       </c>
       <c r="F82" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="83">
@@ -5844,19 +5844,19 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>82.8</v>
+        <v>84.5</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>61.7</v>
+        <v>63.3</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>103.1</v>
+        <v>107.9</v>
       </c>
       <c r="F83" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84">
@@ -5871,19 +5871,19 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>51.9</v>
+        <v>53.4</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>96.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F84" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85">
@@ -5898,19 +5898,19 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>76.2</v>
+        <v>77.7</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>55.9</v>
+        <v>56.1</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="F85" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="86">
@@ -5925,19 +5925,19 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>62</v>
+        <v>63.5</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>84.7</v>
+        <v>86.2</v>
       </c>
       <c r="F86" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87">
@@ -5952,19 +5952,19 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>43.9</v>
+        <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5979,19 +5979,19 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>100.6</v>
+        <v>102.1</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>79.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>122.9</v>
+        <v>123.5</v>
       </c>
       <c r="F88" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="89">
@@ -6006,19 +6006,19 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>70.7</v>
+        <v>70</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>111.6</v>
+        <v>112.9</v>
       </c>
       <c r="F89" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="90">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>59.7</v>
+        <v>61.8</v>
       </c>
       <c r="E90" s="4" t="n">
         <v>103.8</v>
@@ -6045,7 +6045,7 @@
         <v>70.8</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="91">
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>72.8</v>
+        <v>74.2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>94.5</v>
+        <v>97.3</v>
       </c>
       <c r="F91" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92">
@@ -6087,19 +6087,19 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>52.4</v>
+        <v>53.4</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="F92" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93">
@@ -6114,19 +6114,19 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>59.4</v>
+        <v>60.9</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>36.7</v>
+        <v>39.6</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>80</v>
+        <v>84.7</v>
       </c>
       <c r="F93" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94">
@@ -6141,19 +6141,19 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -6168,19 +6168,19 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>74.2</v>
+        <v>78.5</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>120.3</v>
+        <v>121.6</v>
       </c>
       <c r="F95" s="4" t="n">
         <v>70.8</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96">
@@ -6195,19 +6195,19 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>87.2</v>
+        <v>88.7</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>109.4</v>
+        <v>111</v>
       </c>
       <c r="F96" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97">
@@ -6222,19 +6222,19 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>56.9</v>
+        <v>57.1</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>99.5</v>
+        <v>101.6</v>
       </c>
       <c r="F97" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98">
@@ -6249,19 +6249,19 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>47.5</v>
+        <v>48.2</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>92.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F98" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99">
@@ -6276,19 +6276,19 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>91.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F99" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100">
@@ -6303,19 +6303,19 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>56.2</v>
+        <v>57.8</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>34</v>
+        <v>35.5</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>78.8</v>
+        <v>80.3</v>
       </c>
       <c r="F100" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="101">
@@ -6330,19 +6330,19 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>-5.7</v>
+        <v>0</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>39.3</v>
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -6357,19 +6357,19 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>94.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>118.8</v>
+        <v>119.2</v>
       </c>
       <c r="F102" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103">
@@ -6384,19 +6384,19 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>62</v>
+        <v>61.5</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>105.6</v>
+        <v>106.1</v>
       </c>
       <c r="F103" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
@@ -6411,19 +6411,19 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>75.5</v>
+        <v>77.3</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>54.8</v>
+        <v>55.2</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F104" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="105">
@@ -6438,19 +6438,19 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>67</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>44.9</v>
+        <v>46.7</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F105" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106">
@@ -6465,19 +6465,19 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>90.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F106" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109">
@@ -6526,19 +6526,19 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>1641</v>
+        <v>1667</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>999</v>
+        <v>1101</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>2295</v>
+        <v>2244</v>
       </c>
       <c r="E111" s="4" t="n">
         <v>1601</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112">
@@ -6548,19 +6548,19 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1810</v>
+        <v>1819</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1133</v>
+        <v>1228</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>2485</v>
+        <v>2410</v>
       </c>
       <c r="E112" s="4" t="n">
         <v>2093</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="113">
@@ -6570,19 +6570,19 @@
         </is>
       </c>
       <c r="B113" s="4" t="n">
-        <v>2056</v>
+        <v>2008</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1409</v>
+        <v>1465</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>2711</v>
+        <v>2553</v>
       </c>
       <c r="E113" s="4" t="n">
         <v>2124</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="114">
@@ -6592,13 +6592,13 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>1011</v>
+        <v>985</v>
       </c>
       <c r="E114" s="4" t="n">
         <v>2582</v>

--- a/download/predictions_prophet.xlsx
+++ b/download/predictions_prophet.xlsx
@@ -612,22 +612,22 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2537</v>
+        <v>7329</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>6099</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>768</v>
+        <v>2016</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>2582</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -637,22 +637,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>20882</v>
+        <v>27716</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>19837</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>6261</v>
+        <v>8045</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>8400</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -786,16 +786,16 @@
         <v>204</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>119.6</v>
+        <v>117.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>292.4</v>
+        <v>291.4</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
@@ -813,16 +813,16 @@
         <v>173.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>257.5</v>
+        <v>257.7</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -840,16 +840,16 @@
         <v>168</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>255.1</v>
+        <v>259.2</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
@@ -867,16 +867,16 @@
         <v>171.9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>81.3</v>
+        <v>87.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>263</v>
+        <v>260.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9">
@@ -894,16 +894,16 @@
         <v>127.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>222.2</v>
+        <v>217.6</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
@@ -948,16 +948,16 @@
         <v>206.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>117.5</v>
+        <v>122.1</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>287.3</v>
+        <v>294</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -975,16 +975,16 @@
         <v>178.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>269.7</v>
+        <v>268.9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1002,16 +1002,16 @@
         <v>145.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>60.3</v>
+        <v>53</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>239.8</v>
+        <v>241.9</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1029,16 +1029,16 @@
         <v>137.2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>229.2</v>
+        <v>219.1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1056,16 +1056,16 @@
         <v>139.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>49.8</v>
+        <v>46.5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>216</v>
+        <v>226.1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
@@ -1083,16 +1083,16 @@
         <v>94.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>7.9</v>
+        <v>12</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>182.6</v>
+        <v>183.9</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1116,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>176</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>258.7</v>
+        <v>257.9</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
@@ -1164,16 +1164,16 @@
         <v>151.3</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>242.6</v>
+        <v>238.2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
@@ -1191,16 +1191,16 @@
         <v>121.7</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>30.7</v>
+        <v>36.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>200.2</v>
+        <v>214.7</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21">
@@ -1218,16 +1218,16 @@
         <v>118.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>30.1</v>
+        <v>34</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>213.2</v>
+        <v>204.2</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
@@ -1245,16 +1245,16 @@
         <v>127.5</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>42.6</v>
+        <v>41.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>218.9</v>
+        <v>215.6</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23">
@@ -1272,16 +1272,16 @@
         <v>89.8</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>192</v>
+        <v>177.6</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>0</v>
@@ -1326,16 +1326,16 @@
         <v>187.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>105.4</v>
+        <v>105.5</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>273.6</v>
+        <v>279.4</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26">
@@ -1353,16 +1353,16 @@
         <v>171.8</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>81.7</v>
+        <v>88.3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>267.1</v>
+        <v>266.5</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27">
@@ -1380,16 +1380,16 @@
         <v>151.6</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>66.8</v>
+        <v>63.2</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>240.8</v>
+        <v>239.8</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28">
@@ -1407,16 +1407,16 @@
         <v>158.3</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>242.3</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29">
@@ -1434,16 +1434,16 @@
         <v>176.3</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>86.2</v>
+        <v>85</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>261.3</v>
+        <v>259.7</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30">
@@ -1461,16 +1461,16 @@
         <v>147.6</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>48</v>
+        <v>64.8</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>234.9</v>
+        <v>235.7</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>
@@ -1515,16 +1515,16 @@
         <v>261.7</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>174.3</v>
+        <v>179</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>353.6</v>
+        <v>350.1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>208</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
@@ -1542,16 +1542,16 @@
         <v>253.1</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>166.3</v>
+        <v>167.6</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>341.8</v>
+        <v>343.2</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34">
@@ -1569,16 +1569,16 @@
         <v>238.8</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>152.8</v>
+        <v>148.8</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>321.2</v>
+        <v>326.1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>126</v>
+        <v>145.4</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>189</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35">
@@ -1596,16 +1596,16 @@
         <v>250.1</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>158</v>
+        <v>166.1</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>335.6</v>
+        <v>339.6</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36">
@@ -1623,16 +1623,16 @@
         <v>271.5</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>189.8</v>
+        <v>182.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>359.9</v>
+        <v>358.5</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>165</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37">
@@ -1650,16 +1650,16 @@
         <v>244.8</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>157.8</v>
+        <v>149</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>325.8</v>
+        <v>329.5</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38">
@@ -1683,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>164.7</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>0</v>
@@ -1704,16 +1704,16 @@
         <v>358.2</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>273.7</v>
+        <v>265</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>446.8</v>
+        <v>444.8</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40">
@@ -1731,16 +1731,16 @@
         <v>346.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>256</v>
+        <v>257.6</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>433.9</v>
+        <v>431.8</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41">
@@ -1758,16 +1758,16 @@
         <v>328.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>244.3</v>
+        <v>240.9</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>415.8</v>
+        <v>412.9</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42">
@@ -1785,16 +1785,16 @@
         <v>334.1</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>243.5</v>
+        <v>245.1</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>422.4</v>
+        <v>417.9</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43">
@@ -1812,16 +1812,16 @@
         <v>348.5</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>262.1</v>
+        <v>252.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>434.7</v>
+        <v>435.7</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44">
@@ -1839,16 +1839,16 @@
         <v>313.6</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>225.3</v>
+        <v>226.1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>407.1</v>
+        <v>399.8</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45">
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>164.7</v>
+        <v>0</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>0</v>
@@ -1893,16 +1893,16 @@
         <v>407.5</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>322.4</v>
+        <v>326.5</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>498.5</v>
+        <v>494.9</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>247</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47">
@@ -1920,16 +1920,16 @@
         <v>385.4</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>296.6</v>
+        <v>290.5</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>474.3</v>
+        <v>465.1</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>234</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48">
@@ -1947,16 +1947,16 @@
         <v>355.5</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>269.7</v>
+        <v>260</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>442.5</v>
+        <v>445.7</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>216</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49">
@@ -1974,16 +1974,16 @@
         <v>349.7</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>257.4</v>
+        <v>255.6</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>436</v>
+        <v>443.7</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>212</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50">
@@ -2001,16 +2001,16 @@
         <v>352.4</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>265.9</v>
+        <v>268.2</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>440.1</v>
+        <v>440.4</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51">
@@ -2028,16 +2028,16 @@
         <v>306.1</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>222.8</v>
+        <v>224.2</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>397.6</v>
+        <v>396.1</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>186</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52">
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>164.7</v>
+        <v>0</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>0</v>
@@ -2082,16 +2082,16 @@
         <v>378.5</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>299.3</v>
+        <v>288.6</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>472.8</v>
+        <v>468.1</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>230</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54">
@@ -2109,16 +2109,16 @@
         <v>346.7</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>249.6</v>
+        <v>258.6</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>435.5</v>
+        <v>429.6</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55">
@@ -2136,16 +2136,16 @@
         <v>308.1</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>224.4</v>
+        <v>221.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>395.4</v>
+        <v>399.2</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>187</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56">
@@ -2163,16 +2163,16 @@
         <v>294.7</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>205</v>
+        <v>206.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>388.3</v>
+        <v>380.1</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57">
@@ -2190,16 +2190,16 @@
         <v>291.1</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>197.7</v>
+        <v>204.8</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>379.6</v>
+        <v>383.8</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>177</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58">
@@ -2217,16 +2217,16 @@
         <v>239.7</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>150.5</v>
+        <v>156</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>327</v>
+        <v>334.3</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59">
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>164.7</v>
+        <v>0</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>0</v>
@@ -2271,16 +2271,16 @@
         <v>306.2</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>214.7</v>
+        <v>216.5</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>394.2</v>
+        <v>393.5</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>186</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61">
@@ -2298,16 +2298,16 @@
         <v>273.6</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>186.8</v>
+        <v>188.5</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>361.5</v>
+        <v>370.8</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>166</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62">
@@ -2325,16 +2325,16 @@
         <v>235.6</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>146.7</v>
+        <v>147</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>325.2</v>
+        <v>326.5</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63">
@@ -2352,16 +2352,16 @@
         <v>224</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>141</v>
+        <v>134.9</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>313.3</v>
+        <v>310.5</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64">
@@ -2379,16 +2379,16 @@
         <v>223.5</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>143.2</v>
+        <v>138.8</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>313.3</v>
+        <v>307</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65">
@@ -2406,16 +2406,16 @@
         <v>176.3</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>94.8</v>
+        <v>85.7</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>264.9</v>
+        <v>262.7</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>164.7</v>
+        <v>183</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66">
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>167.2</v>
+        <v>0</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>0</v>
@@ -2460,16 +2460,16 @@
         <v>254.1</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>165.8</v>
+        <v>162.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>340.4</v>
+        <v>344.9</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>152</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68">
@@ -2487,16 +2487,16 @@
         <v>228.1</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>313.1</v>
+        <v>313.6</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>136</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69">
@@ -2514,16 +2514,16 @@
         <v>197.2</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>107.9</v>
+        <v>111.3</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>279.5</v>
+        <v>288.1</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70">
@@ -2541,16 +2541,16 @@
         <v>193.1</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>111.1</v>
+        <v>108.9</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>280.6</v>
+        <v>276.7</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71">
@@ -2568,16 +2568,16 @@
         <v>200.1</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>109.5</v>
+        <v>116.3</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>292</v>
+        <v>286.5</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -2595,16 +2595,16 @@
         <v>160.4</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>75.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>241.3</v>
+        <v>246.9</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73">
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>167.2</v>
+        <v>0</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>0</v>
@@ -2649,16 +2649,16 @@
         <v>252.2</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>165.7</v>
+        <v>163.7</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>340.4</v>
+        <v>336.2</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>151</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75">
@@ -2676,16 +2676,16 @@
         <v>232.6</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>148.2</v>
+        <v>146.7</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>322.6</v>
+        <v>321.9</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76">
@@ -2703,16 +2703,16 @@
         <v>207.4</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>121.6</v>
+        <v>122.4</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>291.2</v>
+        <v>294.6</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77">
@@ -2730,16 +2730,16 @@
         <v>208.2</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>120.9</v>
+        <v>118.6</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>294.5</v>
+        <v>298.3</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78">
@@ -2757,16 +2757,16 @@
         <v>219.4</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>133.2</v>
+        <v>132.3</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>296</v>
+        <v>305.6</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79">
@@ -2784,16 +2784,16 @@
         <v>183</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>87.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>273.2</v>
+        <v>271.3</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>109</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>167.2</v>
+        <v>0</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>0</v>
@@ -2838,16 +2838,16 @@
         <v>278.9</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>186.6</v>
+        <v>185.8</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>362.6</v>
+        <v>364.9</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82">
@@ -2865,16 +2865,16 @@
         <v>260</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>173.4</v>
+        <v>171</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>350.9</v>
+        <v>353.1</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>156</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83">
@@ -2892,16 +2892,16 @@
         <v>234.8</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>145.9</v>
+        <v>144.9</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>322.3</v>
+        <v>322.4</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84">
@@ -2919,16 +2919,16 @@
         <v>234.8</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>142.4</v>
+        <v>139.7</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>314.7</v>
+        <v>319.9</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85">
@@ -2946,16 +2946,16 @@
         <v>244.6</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>156</v>
+        <v>156.9</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>331</v>
+        <v>327.6</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="86">
@@ -2973,16 +2973,16 @@
         <v>206.2</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>114.3</v>
+        <v>122.1</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>291.4</v>
+        <v>297</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87">
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>167.2</v>
+        <v>0</v>
       </c>
       <c r="G87" s="4" t="n">
         <v>0</v>
@@ -3027,16 +3027,16 @@
         <v>296.9</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>208.6</v>
+        <v>212.2</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>384.4</v>
+        <v>387.9</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>178</v>
+        <v>148</v>
       </c>
     </row>
     <row r="89">
@@ -3054,16 +3054,16 @@
         <v>275</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>180.8</v>
+        <v>183.5</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>361.1</v>
+        <v>365.8</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="90">
@@ -3081,16 +3081,16 @@
         <v>246.8</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>159.1</v>
+        <v>161.3</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>331</v>
+        <v>336.1</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91">
@@ -3108,16 +3108,16 @@
         <v>243.9</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>149.6</v>
+        <v>152.4</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>326.8</v>
+        <v>332.4</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92">
@@ -3135,16 +3135,16 @@
         <v>250.8</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>161.7</v>
+        <v>159.4</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>342.2</v>
+        <v>341.8</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93">
@@ -3162,16 +3162,16 @@
         <v>209.9</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>120.6</v>
+        <v>124.3</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>291.3</v>
+        <v>305.9</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94">
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>167.2</v>
+        <v>0</v>
       </c>
       <c r="G94" s="4" t="n">
         <v>0</v>
@@ -3216,16 +3216,16 @@
         <v>296.5</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>203.8</v>
+        <v>208</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>384.2</v>
+        <v>382.3</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>167.2</v>
+        <v>200.6</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
     </row>
     <row r="96">
@@ -3243,16 +3243,16 @@
         <v>273.2</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>185.7</v>
+        <v>177.9</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>358.5</v>
+        <v>356</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="97">
@@ -3270,16 +3270,16 @@
         <v>244.1</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>163.5</v>
+        <v>154.8</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>327.3</v>
+        <v>329.1</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98">
@@ -3297,16 +3297,16 @@
         <v>240.8</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>150.5</v>
+        <v>150.8</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>333.3</v>
+        <v>329.6</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99">
@@ -3324,16 +3324,16 @@
         <v>247.9</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>168.3</v>
+        <v>157.8</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>339</v>
+        <v>337.4</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100">
@@ -3351,16 +3351,16 @@
         <v>207.5</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>122.4</v>
+        <v>123.4</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>297.4</v>
+        <v>305.3</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="101">
@@ -3384,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>203.3</v>
+        <v>0</v>
       </c>
       <c r="G101" s="4" t="n">
         <v>0</v>
@@ -3405,16 +3405,16 @@
         <v>296.7</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>214.1</v>
+        <v>204</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>381.9</v>
+        <v>376.6</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>146</v>
+        <v>131</v>
       </c>
     </row>
     <row r="103">
@@ -3432,16 +3432,16 @@
         <v>275.2</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>189.4</v>
+        <v>181</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>362.6</v>
+        <v>364.4</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104">
@@ -3459,16 +3459,16 @@
         <v>248.2</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>156.5</v>
+        <v>159.5</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>335.7</v>
+        <v>340.5</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105">
@@ -3486,16 +3486,16 @@
         <v>247.1</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>158.8</v>
+        <v>157.4</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>335.7</v>
+        <v>339.3</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="106">
@@ -3513,143 +3513,683 @@
         <v>256.5</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>171.1</v>
+        <v>168.1</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>342.4</v>
+        <v>343.4</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>203.3</v>
+        <v>225.9</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>126</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>12/12/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>13/12/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>SYNTHÈSE MENSUELLE</t>
-        </is>
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>14/12/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>312</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>Mois</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Prédiction (t)</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>Borne inf</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Borne sup</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>Objectif (t)</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>% atteinte</t>
-        </is>
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>15/12/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>208.4</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>129</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Sept</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="n">
-        <v>4279</v>
+          <t>16/12/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1996</v>
+        <v>266.7</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>6577</v>
+        <v>177.5</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>3781</v>
+        <v>356.7</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>113</v>
+        <v>225.9</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="n">
-        <v>8250</v>
+          <t>17/12/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>5899</v>
+        <v>266.7</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>10642</v>
+        <v>181.4</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>4942</v>
+        <v>348.5</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>167</v>
+        <v>225.9</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="n">
-        <v>5815</v>
+          <t>18/12/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>3588</v>
+        <v>276.7</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>7959</v>
+        <v>194.9</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>5015</v>
+        <v>367.4</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>116</v>
+        <v>225.9</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
+          <t>19/12/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>20/12/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>21/12/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>330.9</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>22/12/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>220.1</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>395.9</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>23/12/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>282.3</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>189.7</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>24/12/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>25/12/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>26/12/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>246.2</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>27/12/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>28/12/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>254.6</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>423.9</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>29/12/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>306.8</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>394.9</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>30/12/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>275.8</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>172.9</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>SYNTHÈSE MENSUELLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Prédiction (t)</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Borne inf</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Borne sup</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Objectif (t)</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>% atteinte</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Sept</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="n">
+        <v>4279</v>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>2031</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>6572</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>3781</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>5858</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>10623</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>4942</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="n">
+        <v>5815</v>
+      </c>
+      <c r="C133" s="4" t="n">
+        <v>3609</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>8022</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>5015</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
           <t>Déc</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n">
-        <v>2537</v>
-      </c>
-      <c r="C114" s="4" t="n">
-        <v>1680</v>
-      </c>
-      <c r="D114" s="4" t="n">
-        <v>3414</v>
-      </c>
-      <c r="E114" s="4" t="n">
+      <c r="B134" s="4" t="n">
+        <v>7329</v>
+      </c>
+      <c r="C134" s="4" t="n">
+        <v>4935</v>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>9701</v>
+      </c>
+      <c r="E134" s="4" t="n">
         <v>6099</v>
       </c>
-      <c r="F114" s="4" t="n">
-        <v>42</v>
+      <c r="F134" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3663,7 +4203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3741,16 +4281,16 @@
         <v>75.90000000000001</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>55.3</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>97.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6">
@@ -3768,16 +4308,16 @@
         <v>67.09999999999999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>44.7</v>
+        <v>46.8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>88.7</v>
+        <v>90.2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
@@ -3795,16 +4335,16 @@
         <v>58.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -3822,16 +4362,16 @@
         <v>59.6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>37.9</v>
+        <v>39.2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
@@ -3849,16 +4389,16 @@
         <v>45</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>24.2</v>
+        <v>22.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -3882,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0</v>
@@ -3903,16 +4443,16 @@
         <v>83.09999999999999</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>59.4</v>
+        <v>59.1</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>105.5</v>
+        <v>104.7</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3930,16 +4470,16 @@
         <v>72.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>51.8</v>
+        <v>50.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>94.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
@@ -3957,16 +4497,16 @@
         <v>63.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>87.3</v>
+        <v>85.2</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -3984,16 +4524,16 @@
         <v>55</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>33.7</v>
+        <v>34.1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>78.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -4011,16 +4551,16 @@
         <v>56.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>35.4</v>
+        <v>33.1</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>78.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -4038,16 +4578,16 @@
         <v>42</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>21.2</v>
+        <v>19.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>64</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
@@ -4071,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -4092,16 +4632,16 @@
         <v>80.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>101.9</v>
+        <v>103.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>151</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
@@ -4119,16 +4659,16 @@
         <v>70.8</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>92.3</v>
+        <v>93</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
@@ -4146,16 +4686,16 @@
         <v>62.4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>39.7</v>
+        <v>40.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -4173,16 +4713,16 @@
         <v>54.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>31.4</v>
+        <v>32.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>76.5</v>
+        <v>78.2</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
@@ -4200,16 +4740,16 @@
         <v>56.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>34.8</v>
+        <v>34.2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>79.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23">
@@ -4227,16 +4767,16 @@
         <v>42.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>65</v>
+        <v>64.3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24">
@@ -4260,7 +4800,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>0</v>
@@ -4281,16 +4821,16 @@
         <v>82.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>60.3</v>
+        <v>61</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>103.3</v>
+        <v>105.7</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
@@ -4308,16 +4848,16 @@
         <v>73.2</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>51.7</v>
+        <v>49.8</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27">
@@ -4335,16 +4875,16 @@
         <v>65.40000000000001</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>88.5</v>
+        <v>87.3</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
@@ -4362,16 +4902,16 @@
         <v>57.7</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>82.2</v>
+        <v>79.7</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29">
@@ -4392,13 +4932,13 @@
         <v>39.4</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>83.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
@@ -4416,16 +4956,16 @@
         <v>46.8</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>24.2</v>
+        <v>26.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31">
@@ -4449,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>
@@ -4470,16 +5010,16 @@
         <v>87.3</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>110.1</v>
+        <v>109.3</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33">
@@ -4497,16 +5037,16 @@
         <v>78.09999999999999</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34">
@@ -4524,16 +5064,16 @@
         <v>70.3</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>47.2</v>
+        <v>49.4</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>53.4</v>
+        <v>61.6</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
@@ -4551,16 +5091,16 @@
         <v>62.5</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>40.2</v>
+        <v>39.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>86.5</v>
+        <v>84</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36">
@@ -4578,16 +5118,16 @@
         <v>64.59999999999999</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>41.8</v>
+        <v>43.9</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>86.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
@@ -4605,16 +5145,16 @@
         <v>51</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>73.5</v>
+        <v>72.7</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38">
@@ -4638,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>69.8</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>0</v>
@@ -4659,16 +5199,16 @@
         <v>90.59999999999999</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>68.5</v>
+        <v>69.8</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>113.2</v>
+        <v>111.9</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40">
@@ -4686,16 +5226,16 @@
         <v>80.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>59.3</v>
+        <v>61.1</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>103.6</v>
+        <v>103.3</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41">
@@ -4713,16 +5253,16 @@
         <v>72.5</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>51.5</v>
+        <v>52.9</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>95.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42">
@@ -4740,16 +5280,16 @@
         <v>64</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>86.8</v>
+        <v>86.3</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43">
@@ -4767,16 +5307,16 @@
         <v>65.5</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44">
@@ -4797,13 +5337,13 @@
         <v>29.7</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>73.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45">
@@ -4827,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>69.8</v>
+        <v>0</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>0</v>
@@ -4848,16 +5388,16 @@
         <v>89.59999999999999</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>111.1</v>
+        <v>111.8</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47">
@@ -4875,16 +5415,16 @@
         <v>79.3</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>57</v>
+        <v>56.3</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48">
@@ -4902,16 +5442,16 @@
         <v>70.40000000000001</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
@@ -4929,16 +5469,16 @@
         <v>61.5</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>39.3</v>
+        <v>38</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>83.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
@@ -4956,16 +5496,16 @@
         <v>62.8</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>84.3</v>
+        <v>84.8</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
@@ -4983,16 +5523,16 @@
         <v>48.2</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>69.7</v>
+        <v>71.3</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52">
@@ -5016,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>69.8</v>
+        <v>0</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>0</v>
@@ -5037,16 +5577,16 @@
         <v>86.5</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>63.6</v>
+        <v>65</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>108.1</v>
+        <v>109</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54">
@@ -5064,16 +5604,16 @@
         <v>76.3</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>99.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55">
@@ -5091,16 +5631,16 @@
         <v>67.7</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>46.8</v>
+        <v>44.7</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>89.8</v>
+        <v>89.3</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56">
@@ -5118,16 +5658,16 @@
         <v>59.1</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>80.8</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57">
@@ -5145,16 +5685,16 @@
         <v>60.8</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>39.3</v>
+        <v>38.5</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58">
@@ -5172,16 +5712,16 @@
         <v>46.8</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>24.7</v>
+        <v>27.4</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59">
@@ -5205,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>69.8</v>
+        <v>0</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>0</v>
@@ -5226,16 +5766,16 @@
         <v>86.3</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61">
@@ -5253,16 +5793,16 @@
         <v>76.8</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>54.4</v>
+        <v>55.7</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>98</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62">
@@ -5280,16 +5820,16 @@
         <v>68.90000000000001</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>89.2</v>
+        <v>90.7</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63">
@@ -5307,16 +5847,16 @@
         <v>61.1</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>83.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64">
@@ -5334,16 +5874,16 @@
         <v>63.5</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>40.7</v>
+        <v>42.5</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65">
@@ -5361,16 +5901,16 @@
         <v>50.2</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>30.4</v>
+        <v>28.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66">
@@ -5394,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>70.8</v>
+        <v>0</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>0</v>
@@ -5415,16 +5955,16 @@
         <v>91.09999999999999</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>68.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>112.8</v>
+        <v>113.7</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68">
@@ -5442,16 +5982,16 @@
         <v>82.2</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>60.2</v>
+        <v>61.4</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69">
@@ -5469,16 +6009,16 @@
         <v>74.8</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>53.2</v>
+        <v>51.7</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70">
@@ -5496,16 +6036,16 @@
         <v>67.40000000000001</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71">
@@ -5523,16 +6063,16 @@
         <v>70.2</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>48.5</v>
+        <v>46.6</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>92.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72">
@@ -5550,16 +6090,16 @@
         <v>57.1</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>34.5</v>
+        <v>35.4</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>78.7</v>
+        <v>79.7</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73">
@@ -5583,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>70.8</v>
+        <v>0</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>0</v>
@@ -5604,16 +6144,16 @@
         <v>98.09999999999999</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>76.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>120</v>
+        <v>120.7</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75">
@@ -5631,16 +6171,16 @@
         <v>89.09999999999999</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>68.3</v>
+        <v>67.5</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>110</v>
+        <v>110.7</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76">
@@ -5658,16 +6198,16 @@
         <v>81.40000000000001</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>103.9</v>
+        <v>101.1</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77">
@@ -5685,16 +6225,16 @@
         <v>73.8</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>53.7</v>
+        <v>51</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>94</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78">
@@ -5712,16 +6252,16 @@
         <v>76.09999999999999</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>52.9</v>
+        <v>53.6</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>97.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79">
@@ -5739,16 +6279,16 @@
         <v>62.6</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>41.7</v>
+        <v>39.4</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>84.3</v>
+        <v>85.2</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80">
@@ -5772,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>70.8</v>
+        <v>0</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>0</v>
@@ -5793,16 +6333,16 @@
         <v>102.4</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>79.2</v>
+        <v>80</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>124.4</v>
+        <v>123.6</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="82">
@@ -5823,13 +6363,13 @@
         <v>72</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>113.5</v>
+        <v>114.2</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83">
@@ -5847,16 +6387,16 @@
         <v>84.5</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>63.3</v>
+        <v>63.9</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>107.9</v>
+        <v>105.8</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84">
@@ -5880,10 +6420,10 @@
         <v>97.09999999999999</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85">
@@ -5901,16 +6441,16 @@
         <v>77.7</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>56.1</v>
+        <v>56.6</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86">
@@ -5928,16 +6468,16 @@
         <v>63.5</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>86.2</v>
+        <v>84.7</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87">
@@ -5961,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>70.8</v>
+        <v>0</v>
       </c>
       <c r="G87" s="4" t="n">
         <v>0</v>
@@ -5982,16 +6522,16 @@
         <v>102.1</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>80.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>123.5</v>
+        <v>124</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89">
@@ -6009,16 +6549,16 @@
         <v>91.90000000000001</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>70</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>112.9</v>
+        <v>113</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90">
@@ -6036,16 +6576,16 @@
         <v>83.09999999999999</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>103.8</v>
+        <v>103.9</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="91">
@@ -6063,16 +6603,16 @@
         <v>74.2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>52.3</v>
+        <v>54.3</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>97.3</v>
+        <v>96.8</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92">
@@ -6090,16 +6630,16 @@
         <v>75.5</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93">
@@ -6117,16 +6657,16 @@
         <v>60.9</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94">
@@ -6150,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>70.8</v>
+        <v>0</v>
       </c>
       <c r="G94" s="4" t="n">
         <v>0</v>
@@ -6171,16 +6711,16 @@
         <v>99.09999999999999</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>121.6</v>
+        <v>122</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>70.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="96">
@@ -6198,16 +6738,16 @@
         <v>88.7</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>111</v>
+        <v>111.3</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97">
@@ -6225,16 +6765,16 @@
         <v>79.8</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>57.1</v>
+        <v>57.5</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>101.6</v>
+        <v>102.3</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98">
@@ -6252,16 +6792,16 @@
         <v>71</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="99">
@@ -6279,16 +6819,16 @@
         <v>72.3</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="100">
@@ -6306,16 +6846,16 @@
         <v>57.8</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
@@ -6339,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="G101" s="4" t="n">
         <v>0</v>
@@ -6360,16 +6900,16 @@
         <v>96.2</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>73.8</v>
+        <v>74.3</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>119.2</v>
+        <v>117.9</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103">
@@ -6387,16 +6927,16 @@
         <v>86</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>61.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>106.1</v>
+        <v>108.4</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="104">
@@ -6414,16 +6954,16 @@
         <v>77.3</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>55.2</v>
+        <v>56</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105">
@@ -6441,16 +6981,16 @@
         <v>68.59999999999999</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>90.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106">
@@ -6468,143 +7008,683 @@
         <v>70.09999999999999</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>81</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>12/12/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>13/12/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>SYNTHÈSE MENSUELLE</t>
-        </is>
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>14/12/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>Mois</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Prédiction (t)</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>Borne inf</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Borne sup</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>Objectif (t)</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>% atteinte</t>
-        </is>
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>15/12/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Sept</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="n">
-        <v>1667</v>
+          <t>16/12/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1101</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>2244</v>
+        <v>54.3</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1601</v>
+        <v>98.2</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>104</v>
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="n">
-        <v>1819</v>
+          <t>17/12/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1228</v>
+        <v>67.3</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>2410</v>
+        <v>46.8</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>2093</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>87</v>
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="n">
-        <v>2008</v>
+          <t>18/12/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1465</v>
+        <v>68.8</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>2553</v>
+        <v>47.1</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>2124</v>
+        <v>91</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>95</v>
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
+          <t>19/12/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>20/12/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>21/12/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>22/12/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>23/12/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>24/12/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>25/12/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>26/12/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>27/12/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>28/12/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>29/12/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>30/12/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>SYNTHÈSE MENSUELLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Prédiction (t)</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Borne inf</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Borne sup</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Objectif (t)</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>% atteinte</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Sept</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="n">
+        <v>1667</v>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>1099</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>2247</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>1601</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n">
+        <v>1819</v>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>1239</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>2407</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>2093</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C133" s="4" t="n">
+        <v>1461</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>2553</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>2124</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
           <t>Déc</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n">
-        <v>768</v>
-      </c>
-      <c r="C114" s="4" t="n">
-        <v>542</v>
-      </c>
-      <c r="D114" s="4" t="n">
-        <v>985</v>
-      </c>
-      <c r="E114" s="4" t="n">
+      <c r="B134" s="4" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C134" s="4" t="n">
+        <v>1428</v>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>2615</v>
+      </c>
+      <c r="E134" s="4" t="n">
         <v>2582</v>
       </c>
-      <c r="F114" s="4" t="n">
-        <v>30</v>
+      <c r="F134" s="4" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
